--- a/dados/orcamentos_tematicos/crianca_adolescente/OCA_QUADRIMESTRE/2024/ot-oca-3-quad-2024-versao-1.xlsx
+++ b/dados/orcamentos_tematicos/crianca_adolescente/OCA_QUADRIMESTRE/2024/ot-oca-3-quad-2024-versao-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\pbh_visualizacao_de_dados\dados\orcamentos_tematicos\crianca_adolescente\OCA_QUADRIMESTRE\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887A2A27-1C7F-4A62-934A-D416D00BC231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3975572-D207-4D62-8DDC-496B4C50FFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24194,22 +24194,10 @@
       <c r="T357" s="4"/>
     </row>
     <row r="358" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="Q358" s="5">
-        <f>SUM(Q3:Q357)</f>
-        <v>5210021442.0500002</v>
-      </c>
-      <c r="R358" s="5">
-        <f t="shared" ref="R358:T358" si="0">SUM(R3:R357)</f>
-        <v>5468966624.7735014</v>
-      </c>
-      <c r="S358" s="5">
-        <f t="shared" si="0"/>
-        <v>5254387539.9860029</v>
-      </c>
-      <c r="T358" s="5">
-        <f t="shared" si="0"/>
-        <v>4955334050.4734993</v>
-      </c>
+      <c r="Q358" s="5"/>
+      <c r="R358" s="5"/>
+      <c r="S358" s="5"/>
+      <c r="T358" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
